--- a/data/seed/portfolio/L-2024-8895/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-8895/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -560,31 +560,31 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>3076000</v>
+        <v>7968000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №119/26 от 02.07.2026</t>
+          <t>Предоплата за товар по договору №26/26 от 01.07.2026</t>
         </is>
       </c>
     </row>
@@ -601,21 +601,21 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>15571000</v>
+        <v>11121000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navro'z Tikuv XK</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>322881518</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000376255309001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4480 от 03.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №7665 от 03.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -640,33 +640,33 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>1226000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>6566000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sarbon Agro Servis MChJ</t>
+          <t>Nurafshon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>217106795</t>
+          <t>338718986</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000613231154001</t>
+          <t>20208000508227263001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7931</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №173/26 ОТ 03.07.026</t>
         </is>
       </c>
     </row>
@@ -681,33 +681,33 @@
           <t>103</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>4624000</v>
-      </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>925000</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sarbon Agro Servis MChJ</t>
+          <t>Angren Polimer AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>217106795</t>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000613231154001</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2238</t>
+          <t>Предоплата за товар по дог. №77/26 от 03.07.2026</t>
         </is>
       </c>
     </row>
@@ -724,21 +724,21 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>10603000</v>
+        <v>23577000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Angren Polimer AJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2773 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6987 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -765,31 +765,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>7612000</v>
+        <v>14159000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №211/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №249/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -806,31 +806,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>4595000</v>
+        <v>3749000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Shodlik Moy XK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>246801308</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000814267951001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №106/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №216/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
@@ -845,33 +845,33 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>2402000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>1720000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Angren Polimer AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №742</t>
+          <t>Mahsulot uchun o'lov, shartn. №57/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -886,28 +886,33 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>9020000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>1039000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №4725</t>
+          <t>Оплата за товар по счет-фактуре №742 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -922,40 +927,40 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>49838000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>1032000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Qarshi Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>334970339</t>
+          <t>288151893</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000068136382001</t>
+          <t>20208000625530999001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №3/26 от 06.07.2026, НДС 12%</t>
+          <t>Предоплата за товар по дог. №278/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -964,39 +969,39 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>3084000</v>
+        <v>3611000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №28/26 от 07.07.2026, НДС 12%</t>
+          <t>Предоплата за материалы по договору №234/26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1005,39 +1010,34 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1060000</v>
+        <v>9020000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahor Qurilish AJ</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>244310572</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000944858456001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по дог. №12/22</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,23 +1045,23 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>3493000</v>
-      </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>5798000</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Urganch Yog'och XK</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>310744620</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000208243824001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1071,14 +1071,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №197/26 от 08.07.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5688 от 07.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1088,38 +1088,38 @@
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>9814000</v>
+        <v>4451000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №4285 ОТ 10.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №117/26 от 07.07.2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1129,38 +1129,38 @@
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>26072000</v>
+        <v>2052000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Navro'z Tikuv XK</t>
+          <t>Angren Polimer AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>322881518</t>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000376255309001</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5491 13.07.2026, QQS bilan</t>
+          <t>Оплата за товар по с/ф №8279 от 07.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1170,38 +1170,38 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>16196000</v>
+        <v>2003000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Namangan Plastik XK</t>
+          <t>Lazzat Qurilish MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>267394515</t>
+          <t>310679586</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000696289072001</t>
+          <t>20208000323115473001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6631 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №123 от 08.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1209,40 +1209,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>3355000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Xiva Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>340769130</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000639542497001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5087 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Аренда помещения за июль, дог. №91/23</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1252,38 +1252,38 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>9970000</v>
+        <v>2578000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4886</t>
+          <t>Предоплата за товар по договору №152/26 от 09.07.2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1291,40 +1291,40 @@
           <t>118</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>5033000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>12378000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Chust Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>314557650</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000300741277001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №163/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №269/26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1334,38 +1334,38 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>2606000</v>
+        <v>1537000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №143/26 от 16.07.2026</t>
+          <t>Оплата по счет-фактуре №7158 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1374,39 +1374,39 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1230000</v>
+        <v>8427000</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Urganch Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>274462092</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000824382424001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Предоплата за материалы по договору №201/26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1415,39 +1415,39 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1230000</v>
+        <v>10483000</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ilhom Tekstil AJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>385800104</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000988469332001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №1/26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1457,38 +1457,38 @@
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>7035000</v>
+        <v>2627000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3543 20.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №134/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1496,40 +1496,40 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>6973000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>4562000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Chust Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>314557650</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000300741277001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №726 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №61/26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1537,40 +1537,40 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>4519000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>1230000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №221/26, НДС 12%</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1579,39 +1579,39 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>2109000</v>
+        <v>1230000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>334970339</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000068136382001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №268/26 от 20.07.2026, НДС 12%</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1619,40 +1619,40 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>2610000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>8805000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Savdo MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>282904290</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000907374034001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №98/26 от 20.07.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №18/26 от 16.07.2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1660,40 +1660,40 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>4957000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>3579000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Gulshan Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>334970339</t>
+          <t>285568381</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000068136382001</t>
+          <t>20208000949092629001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5020</t>
+          <t>Оплата по с/ф №2435 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1701,40 +1701,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>6249000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>18639000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9709 от 21.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №535</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1742,23 +1742,23 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>1478000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>1945000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Qarshi Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>288151893</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000625530999001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1768,14 +1768,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2650</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №920</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>7158000</v>
+        <v>1339000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1468 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №68/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1824,23 +1824,23 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>662000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>5047000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000317392683001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1850,14 +1850,14 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Предоплата за товар по договору №131/26 от 20.07.2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1865,40 +1865,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>1757000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>962000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Оплата по с/ф №5605 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1906,35 +1906,40 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>20200000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>900000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8895)</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>16307000375545878417</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8895 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Shartnoma №21/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1943,39 +1948,39 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>2707000</v>
+        <v>7925000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTN. №280/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №9830</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1988,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>23408000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>2825000</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1904</t>
+          <t>Mahsulot uchun to'lov, shartnoma №217/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2025,17 +2030,22 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>300000</v>
+        <v>8198000</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Urganch Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>274462092</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000824382424001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2045,14 +2055,14 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за товары согласно счет-фактуре №2073</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2060,40 +2070,40 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>1916000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>4401000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>334970339</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000068136382001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4533</t>
+          <t>Shartnoma №23/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2101,40 +2111,40 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>10630000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>3192000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №82/26 от 31.07.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5445 от 23.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2142,40 +2152,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>4684000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>1694000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №105/26 от 03.08.2026</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2185,38 +2195,38 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>4146000</v>
+        <v>1691000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5294 03.08.2026, QQS bilan</t>
+          <t>Оплата по с/ф №6687 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2226,38 +2236,38 @@
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>3807000</v>
+        <v>1209000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Gulshan Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>285568381</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000949092629001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5970 03.08.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №9101 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2265,40 +2275,40 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>2868000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>12425000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Namangan Plastik XK</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>267394515</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000696289072001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №104/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №117/26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>25.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2306,40 +2316,35 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>2311000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>20200000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>335933854</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8895)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>16307000375545878417</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №63/26 от 03.08.2026</t>
+          <t>Kredit shartnomasi L-2024-8895 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2349,38 +2354,38 @@
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>1576000</v>
+        <v>3630000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9068 ОТ 03.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Предоплата за товар по дог. №291/26 от 27.07.2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2388,40 +2393,40 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>701000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>1858000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №139/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №39/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2430,39 +2435,39 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>2815000</v>
+        <v>662000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000623690163001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7146</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2471,39 +2476,39 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>3174000</v>
+        <v>7768000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7084</t>
+          <t>Оплата за сырье по договору №165/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2512,39 +2517,39 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>5522000</v>
+        <v>20854000</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №1/26 от 03.08.2026, НДС 12%</t>
+          <t>Предоплата за материалы по дог №50/26</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2552,35 +2557,40 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>9891000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>3402000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9037 29.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2590,21 +2600,21 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>8918000</v>
+        <v>3471000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Navro'z Tikuv XK</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>322881518</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000376255309001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2614,14 +2624,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9546 ОТ 06.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №4803 от 31.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2629,40 +2639,35 @@
           <t>151</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>7660000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tur Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>302946003</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000713461733001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2037 за поставленный товар</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2672,38 +2677,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>3440000</v>
+        <v>8968000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4252</t>
+          <t>Предоплата за товар по договору №90/26 от 03.08.2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2713,38 +2718,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>6382000</v>
+        <v>7362000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №293/26 от 10.08.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2816</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2754,38 +2759,38 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>3981000</v>
+        <v>8620000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №108 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №15/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2793,40 +2798,40 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n">
-        <v>3063000</v>
-      </c>
+      <c r="C65" s="2" t="n">
+        <v>397000</v>
+      </c>
+      <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №126/26 от 10.08.2026</t>
+          <t>Предоплата за материалы по договору №285/26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2835,39 +2840,39 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>1017000</v>
+        <v>1791000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sarbon Agro Servis MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>217106795</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000613231154001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №128/26</t>
+          <t>Оплата за транспортные услуги по дог. №274/26</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2876,39 +2881,39 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1162000</v>
+        <v>116967000</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bahor Qurilish AJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>244310572</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000944858456001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov avgust</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №293/26</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2917,39 +2922,39 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>65061000</v>
+        <v>330000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Urganch Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>274462092</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000824382424001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №141/26</t>
+          <t>Xom ashyo uchun to'lov, shartn. №72/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2957,40 +2962,35 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>1426000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>9891000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>382975006</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №83/26, НДС 12%</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №7838</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2999,39 +2999,39 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>2679000</v>
+        <v>816000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Sarbon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>334970339</t>
+          <t>383321485</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000068136382001</t>
+          <t>20208000315177947001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №129/26, QQS bilan</t>
+          <t>Оплата за упаковчные материалы, с/ф №9494</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3041,38 +3041,38 @@
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>1806000</v>
+        <v>9467000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1996 12.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №175/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3080,40 +3080,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>1417000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>1162000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Xiva Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>340769130</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000639542497001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7335 за поставленный товар</t>
+          <t>Аренда помещения за август, дог. №91/23</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3121,40 +3121,40 @@
           <t>163</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>4160000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>289000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Saodat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>383624861</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000025772161001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2255 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Предоплата за материалы по договору №170/26</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3162,33 +3162,33 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>3611000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>361000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zafar Avto Ehtiyot MChJ</t>
+          <t>Oltin Vodiy Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>228962686</t>
+          <t>210572794</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000517388604001</t>
+          <t>20208000858456931001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1426 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по дог. №20/26</t>
         </is>
       </c>
     </row>
@@ -3204,32 +3204,32 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>8520000</v>
+        <v>166000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №217/26</t>
+          <t>Оплата за сырье по договору №145/26 от 14.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3246,31 +3246,31 @@
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>3219000</v>
+        <v>5001000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО С/Ф №247 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за продукцию по договору №297/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3285,23 +3285,23 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>701000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>2590000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oydin Dori-Darmon MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>321855683</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000109490926001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №91/26</t>
+          <t>Оплата за товар по счет-фактуре №7569 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3327,32 +3327,32 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>1349000</v>
+        <v>176000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oltin Vodiy Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>210572794</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000858456931001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №132/26</t>
         </is>
       </c>
     </row>
@@ -3368,39 +3368,39 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1349000</v>
+        <v>218000</v>
       </c>
       <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chust Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>314557650</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000300741277001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Предоплата за материалы по договору №22/26</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3408,40 +3408,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>6398000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>366000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Oltin Vodiy Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>210572794</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000858456931001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7295</t>
+          <t>Оплата за сырье по дог. №27/26 от 17.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3449,40 +3449,40 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>2193000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>1349000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3972 за поставленный товар</t>
+          <t>Ijtimoiy soliq iyul 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3491,39 +3491,39 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>2669000</v>
+        <v>1349000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №146/26</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3533,38 +3533,38 @@
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>14399000</v>
+        <v>1515000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №189/26 от 20.08.2026</t>
+          <t>Предоплата за товар по договору №120/26 от 18.08.2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3572,33 +3572,33 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>1894000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>1664000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Polimer MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>294600317</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000346173339001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4844</t>
         </is>
       </c>
     </row>
@@ -3614,32 +3614,32 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>2217000</v>
+        <v>2011000</v>
       </c>
       <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №204/26</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
@@ -3656,21 +3656,21 @@
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>2747000</v>
+        <v>59757000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Navro'z Tikuv XK</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>322881518</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000376255309001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №272/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №171/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
@@ -3695,33 +3695,33 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>743000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>14885000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Namangan Sut XK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>253469150</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000642378059001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2740</t>
+          <t>Предоплата за товар по дог. №39/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
@@ -3737,32 +3737,32 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>1007000</v>
+        <v>249000</v>
       </c>
       <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Urganch Yog'och XK</t>
+          <t>Urganch Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>310744620</t>
+          <t>274462092</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000208243824001</t>
+          <t>20208000824382424001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №67/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №5449</t>
         </is>
       </c>
     </row>
@@ -3778,32 +3778,32 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>1728000</v>
+        <v>726000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oydin Dori-Darmon MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>321855683</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000109490926001</t>
+          <t>20208000623690163001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8857</t>
+          <t>ELEKTR ENERGIYASI UCHUN TO'LOV</t>
         </is>
       </c>
     </row>
@@ -3819,32 +3819,32 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>2286000</v>
+        <v>877000</v>
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5571</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГ. №272/26</t>
         </is>
       </c>
     </row>
@@ -3860,39 +3860,39 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>2929000</v>
+        <v>1158000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Oltin Vodiy Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>210572794</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000858456931001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №109</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №6047</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3900,33 +3900,33 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>4091000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>5456000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Urganch Yog'och XK</t>
+          <t>Gulshan Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>310744620</t>
+          <t>285568381</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000208243824001</t>
+          <t>20208000949092629001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №4192</t>
+          <t>Предоплата за товар по договору №11/26 от 25.08.2026</t>
         </is>
       </c>
     </row>
@@ -3941,40 +3941,35 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>29587000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>20200000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Navro'z Tikuv XK</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>322881518</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8895)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000376255309001</t>
+          <t>16307000375545878417</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Shartnoma №45/26 bo'yicha oldindan to'lov</t>
+          <t>Kredit shartnomasi L-2024-8895 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3982,28 +3977,33 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>20200000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>24941000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8895)</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>16307000375545878417</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8895 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата по счет-фактуре №1202 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -4020,21 +4020,21 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>2666000</v>
+        <v>6279000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Angren Polimer AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4044,14 +4044,14 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9951 от 26.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №2188 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4059,40 +4059,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>726000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>3600000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bahor Agro MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>297033920</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000317392683001</t>
+          <t>20208000813638253001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>ELEKTR ENERGIYASI UCHUN TO'LOV AVGUST</t>
+          <t>Предоплата за товар по договору №39/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4102,38 +4102,38 @@
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>2563000</v>
+        <v>2633000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8836</t>
+          <t>Предоплата за товар по договору №71/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4143,38 +4143,38 @@
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>16071000</v>
+        <v>2588000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3902 от 28.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №57/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4184,38 +4184,38 @@
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>3274000</v>
+        <v>2252000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Lazzat Polimer MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>294600317</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000346173339001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №415 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №282/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,33 +4223,28 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>2458000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>335933854</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1364 от 28.08.2026, в т.ч. НДС 12%</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
@@ -4264,23 +4259,23 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>4782000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>1924000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Ilhom Tekstil AJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>385800104</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000988469332001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4290,14 +4285,14 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №288/26 от 31.08.2026</t>
+          <t>Оплата за сырье по договору №281/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4307,38 +4302,38 @@
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>2217000</v>
+        <v>4275000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8372 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №1565 от 01.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4347,34 +4342,39 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>300000</v>
+        <v>1478000</v>
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Ilhom Tekstil AJ</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>385800104</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000988469332001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Tovarlar uchun to'lov h/f №9076</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4382,23 +4382,23 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>1514000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>1578000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oydin Dori-Darmon MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>321855683</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000109490926001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4408,14 +4408,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №67/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №7843 от 02.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4423,40 +4423,40 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>2411000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>5081000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Angren Polimer AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4686</t>
+          <t>Оплата за товар по счет-факуре №2186 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4464,40 +4464,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>2525000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>1316000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>334970339</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000068136382001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №268/26 от 31.08.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №1461 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4505,23 +4505,23 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>10912000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>2955000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sarbon Agro Servis MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>217106795</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000613231154001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4531,14 +4531,14 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3305</t>
+          <t>Tovar uchun to'lov, h/f №8011 07.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4548,38 +4548,38 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>7283000</v>
+        <v>2265000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №9866 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за товар по счет-фактуре №9823 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4589,38 +4589,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>5310000</v>
+        <v>2083000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №28/26 от 03.09.2026</t>
+          <t>Оплата по счет-фактуре №5280 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4630,38 +4630,38 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>4366000</v>
+        <v>1825000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Qarshi Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>288151893</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000625530999001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5670 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №299/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4669,40 +4669,40 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>2297000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>1635000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8994</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8634 07.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4710,33 +4710,33 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>3529000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>1370000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Lazzat Polimer MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>334970339</t>
+          <t>294600317</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000068136382001</t>
+          <t>20208000346173339001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №121/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №6462 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -4751,33 +4751,33 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>9301000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>2870000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4839 за поставленный товар</t>
+          <t>Оплата за упаковочные материалы, с/ф №4189</t>
         </is>
       </c>
     </row>
@@ -4792,40 +4792,35 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>6199000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>10185000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Navro'z Tikuv XK</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>322881518</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000376255309001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3728</t>
+          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4834,39 +4829,39 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>872000</v>
+        <v>1197000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Urganch Yog'och XK</t>
+          <t>Xiva Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>310744620</t>
+          <t>340769130</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000208243824001</t>
+          <t>20208000639542497001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3069</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №91/23</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4874,40 +4869,40 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>1197000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>2268000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bahor Qurilish AJ</t>
+          <t>Angren Polimer AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>244310572</t>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000944858456001</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №12/22</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8139</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4915,35 +4910,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>10185000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>2195000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №2305</t>
+          <t>Оплата за товар по счет-фактуре №4843 от 09.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4953,38 +4953,38 @@
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>15160000</v>
+        <v>2029000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №600 от 09.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №292/26 от 10.09.2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4992,23 +4992,23 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>1645000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>1348000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Savdo MChJ</t>
+          <t>Angren Polimer AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>282904290</t>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000907374034001</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5018,14 +5018,14 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №689</t>
+          <t>Mahsulot uchun to'lov, shartnoma №116/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5034,39 +5034,39 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>9806000</v>
+        <v>4478000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Urganch Yog'och XK</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>310744620</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000208243824001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №283/26</t>
+          <t>Предоплата за материалы по договору №106/26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5074,23 +5074,23 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>12166000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>7981000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oydin Dori-Darmon MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>321855683</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000109490926001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5100,14 +5100,14 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №241/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3705 14.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5117,31 +5117,31 @@
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>4759000</v>
+        <v>6452000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3610 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №107/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -5158,31 +5158,31 @@
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>41192000</v>
+        <v>2918000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5739 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №5176 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -5199,21 +5199,21 @@
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>12792000</v>
+        <v>1461000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Angren Polimer AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9108 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №1372 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -5239,32 +5239,32 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>2141000</v>
+        <v>1389000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №6/26</t>
+          <t>Avgustoyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
@@ -5280,32 +5280,32 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>5534000</v>
+        <v>1389000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товры согласно с/ф №410</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
     </row>
@@ -5321,39 +5321,39 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>9384000</v>
+        <v>2179000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sarbon Agro Servis MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>217106795</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000613231154001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №257/26 от 14.09.2026, НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №609</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5362,39 +5362,39 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>1221000</v>
+        <v>4414000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №251/26</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №143/26</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5403,39 +5403,39 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>1236000</v>
+        <v>78947000</v>
       </c>
       <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Ilhom Tekstil AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>385800104</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000988469332001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3133</t>
+          <t>Оплата за транспортные услуги по договору №179/26</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5443,40 +5443,40 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>1389000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>5097000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Gulshan Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>285568381</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000949092629001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Shartnoma №6/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5485,39 +5485,39 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1389000</v>
+        <v>2980000</v>
       </c>
       <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oltin Vodiy Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>210572794</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000858456931001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №96/26</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5527,38 +5527,38 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>26951000</v>
+        <v>2107000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tur Servis MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>302946003</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000713461733001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Shartnoma №257/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №168/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5566,40 +5566,40 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>3832000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>1377000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №227/26</t>
+          <t>Оплата за продукцию по дог. №38/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5607,40 +5607,40 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>3908000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>4221000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №38/26</t>
+          <t>Оплата за товар по с/ф №1032 от 18.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5648,40 +5648,40 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>4487000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>1203000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Namangan Sut XK</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>253469150</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000642378059001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1697</t>
+          <t>Оплата за продукцию по дог. №209/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5689,33 +5689,33 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>2583000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>4598000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Angren Polimer AJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплат за товары согласно счет-фактуре №4821</t>
+          <t>Оплата за товар по счет-фактуре №1350 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -5732,38 +5732,38 @@
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>5407000</v>
+        <v>1658000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №284/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №169/26 от 21.09.2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5773,38 +5773,38 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>4120000</v>
+        <v>3466000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Shartnoma №248/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №4504 от 22.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5814,38 +5814,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>3356000</v>
+        <v>1431000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №28/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №122 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5854,39 +5854,39 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>1112000</v>
+        <v>1950000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №5897</t>
+          <t>НДС за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5894,40 +5894,40 @@
           <t>231</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>1973000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>21305000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>288151893</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000625530999001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3388 23.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5936,32 +5936,32 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>13700000</v>
+        <v>4717000</v>
       </c>
       <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Oltin Vodiy Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>210572794</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000858456931001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1167</t>
+          <t>Оплата за сырье по дог. №270/26 от 23.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -5976,40 +5976,40 @@
           <t>233</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>28613000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>1276000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Oydin Dori-Darmon MChJ</t>
+          <t>Nurafshon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>321855683</t>
+          <t>338718986</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000109490926001</t>
+          <t>20208000508227263001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата затовары согласно счет-фактуре №2091</t>
+          <t>Оплата за товар по с/ф №4107 от 24.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6019,38 +6019,38 @@
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>5357000</v>
+        <v>1041000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Termiz Savdo AJ</t>
+          <t>Angren Polimer AJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>382975006</t>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000968922762001</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2985 за поставленный товар</t>
+          <t>Предоплата за товар по договору №203/26 от 24.09.2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6059,32 +6059,32 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>748000</v>
+        <v>800000</v>
       </c>
       <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000317392683001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+          <t>Оплата за сырье по дог. №224/26 от 24.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -6099,35 +6099,40 @@
           <t>236</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n">
-        <v>20200000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n">
+        <v>15904000</v>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8895)</t>
+          <t>Angren Polimer AJ</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>297500649</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>16307000375545878417</t>
+          <t>20208000892276200001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8895 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата по счет-фактуре №790 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6137,38 +6142,38 @@
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>12831000</v>
+        <v>3925000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Andijon Qog'oz MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>335933854</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000185239259001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №99/26 от 28.09.2026</t>
+          <t>Оплата по счет-фактуре №232 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6176,40 +6181,40 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
-        <v>6785000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>1707000</v>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>334970339</t>
+          <t>393385451</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000068136382001</t>
+          <t>20208000523925936001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №48/26</t>
+          <t>Оплата за товар по с/ф №6971 от 25.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6218,39 +6223,39 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>5421000</v>
+        <v>3461000</v>
       </c>
       <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Oltin Vodiy Mebel AJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>290429069</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000737403407001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3552</t>
+          <t>Оплата за транспортные услуги по договору №178/26</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6259,17 +6264,17 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>300000</v>
+        <v>20200000</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8895)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>16307000375545878417</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6279,14 +6284,14 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Kredit shartnomasi L-2024-8895 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6294,59 +6299,628 @@
           <t>241</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
-        <v>9564000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>13356000</v>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz MChJ</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>234186970</t>
+          <t>396268635</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000035287194001</t>
+          <t>20208000738860482001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9088</t>
+          <t>Оплата за продукцию по договору №50/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="n">
-        <v>479251000</v>
-      </c>
-      <c r="D152" s="4" t="n">
-        <v>468651000</v>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>5773000</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Lazzat Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>294600317</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20208000346173339001</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №162/26 от 28.09.2026</t>
+        </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>5698000</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Angren Polimer AJ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>297500649</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>20208000892276200001</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №231/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>2150000</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Bahor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>393385451</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000523925936001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №265/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n">
+        <v>1357000</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Bahor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>393385451</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20208000523925936001</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №59/26 от 28.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>746000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Oltin Vodiy Mebel AJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>290429069</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000737403407001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №53/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>748000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000623690163001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>18904000</v>
+      </c>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Oltin Vodiy Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>210572794</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000858456931001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №142/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>5162000</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Bahor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>393385451</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000523925936001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №97/26 от 29.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>2258000</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Angren Polimer AJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>297500649</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000892276200001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №17/26 от 29.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>796000</v>
+      </c>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Oltin Vodiy Mebel AJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>290429069</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000737403407001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №238/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>1216000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Urganch Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>274462092</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000824382424001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №283/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>5382000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Bahor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>393385451</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000523925936001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №124/26 от 30.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Navbahor Bank ATB</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Плата за SMS-информирование</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>2740000</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Urganch Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>274462092</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000824382424001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №212/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="n">
+        <v>481823000</v>
+      </c>
+      <c r="D166" s="4" t="n">
+        <v>471223000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C153" s="4" t="n">
+      <c r="C167" s="4" t="n">
         <v>89300000</v>
       </c>
-      <c r="D153" s="4" t="n"/>
+      <c r="D167" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
